--- a/ipo-analysis/companies/tonbo-imaging-india-ltd/TONBO_IMAGING_INDIA_LTD_01_Screening.xlsx
+++ b/ipo-analysis/companies/tonbo-imaging-india-ltd/TONBO_IMAGING_INDIA_LTD_01_Screening.xlsx
@@ -2429,17 +2429,17 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>p. 90</t>
+          <t>pp. 23, 90</t>
         </is>
       </c>
       <c r="G6" s="27" t="inlineStr">
         <is>
-          <t>CFO Rs 783.33 m / -1,361.19 m / -632.16 m FY24-26 and -146.83 m in Q1 FY27, against PAT 685.43 / 727.57 / 508.80 / -177.37. Cumulative CFO/PAT FY24-26 = -63.0%. Working-capital days 152 -&gt; 280 -&gt; 517 (p. 144).</t>
+          <t>Operating cash flow Rs 783.33 m in FY24, then -1,361.19 m (FY25, incl. the final instalments for the IP purchase) and -632.16 m (FY26) as export orders were deferred and stock was built for FY27 orders (pp. 23, 25, 439). Cumulative CFO/PAT FY24-26 -63.0%. A timing item in a lumpy order cycle; track H1 FY27 cash flow.</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="G8" s="27" t="inlineStr">
         <is>
-          <t>IP bought from CEAQ Singapore (formerly Tonbo Imaging Pte; an enterprise with substantial interest, selling shareholder) for Rs 1,831.91 m in Mar-2024, valued by DCF (MPEEM, 10-year life) and capitalised: 54.4% of FY24 total expenses. Material purchases from CEAQ Singapore continue: Rs 789.80 m in FY26 (26.3% of total expenses) and Rs 171.99 m in Q1 FY27 (28.2%).</t>
+          <t>Disclosed related-party dealings with CEAQ Singapore (former parent): the one-time IP purchase of Rs 1,831.91 m in FY24, valued by DCF and paid in instalments, which removed future royalties; and material purchases of Rs 789.80 m in FY26 (26.3% of total expenses). Track the share of purchases from CEAQ after listing.</t>
         </is>
       </c>
     </row>
